--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487943_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487943_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>P. CARRASCO LOBO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0903</v>
+        <v>2.1432</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.5546</v>
+        <v>-1.2507</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6448</v>
+        <v>3.3939</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0518</v>
+        <v>0.2472</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.1152</v>
+        <v>-0.9887</v>
       </c>
       <c r="I2" t="n">
-        <v>1.167</v>
+        <v>1.2359</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.1165</v>
+        <v>-0.597</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.1968</v>
+        <v>-0.6048</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0804</v>
+        <v>0.0078</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1683</v>
+        <v>0.8442</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08160000000000001</v>
+        <v>-0.3839</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0866</v>
+        <v>1.2281</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.3964</v>
       </c>
       <c r="R2" t="n">
-        <v>1.784</v>
+        <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1841</v>
+        <v>0.3102</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3082</v>
+        <v>-0.5238</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4923</v>
+        <v>0.834</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>0.2666</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7997</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0436</v>
+        <v>1.6995</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4439</v>
+        <v>-0.6476</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4875</v>
+        <v>2.3471</v>
       </c>
       <c r="G3" t="n">
         <v>0.95</v>
@@ -688,13 +688,13 @@
         <v>1.1893</v>
       </c>
       <c r="S3" t="n">
-        <v>0.49</v>
+        <v>0.1459</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3082</v>
+        <v>-0.5119</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7982</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0.6036</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. CARRASCO LOBO</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1087</v>
+        <v>1.4788</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.0886</v>
+        <v>-1.4922</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1973</v>
+        <v>2.9709</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2472</v>
+        <v>0.0518</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9887</v>
+        <v>-1.1152</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2359</v>
+        <v>1.167</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.597</v>
+        <v>-1.1165</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6048</v>
+        <v>-1.1968</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0078</v>
+        <v>0.0804</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8442</v>
+        <v>1.1683</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3839</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2281</v>
+        <v>1.0866</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.3964</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9822</v>
+        <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7243000000000001</v>
+        <v>0.5726</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3617</v>
+        <v>-0.2458</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6375</v>
+        <v>0.8184</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
       <c r="W4" t="n">
         <v>0.2666</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2666</v>
+        <v>-0.7997</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.099</v>
+        <v>-0.5573</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7981</v>
+        <v>-2.2845</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6991</v>
+        <v>1.7272</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3601</v>
@@ -844,13 +844,13 @@
         <v>1.3876</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2522</v>
+        <v>0.7938</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7564</v>
+        <v>0.2699</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4958</v>
+        <v>0.5239</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ SANCHEZ</t>
+          <t>L. MORENO MORALES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7357</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7453</v>
+        <v>0.399</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.481</v>
+        <v>-1.0608</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6831</v>
+        <v>-0.0169</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9188</v>
+        <v>0.1762</v>
       </c>
       <c r="I6" t="n">
-        <v>2.602</v>
+        <v>-0.1931</v>
       </c>
       <c r="J6" t="n">
-        <v>3.154</v>
+        <v>0.1538</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0202</v>
+        <v>0.9016</v>
       </c>
       <c r="L6" t="n">
-        <v>3.1339</v>
+        <v>-0.7478</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4709</v>
+        <v>-0.1708</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9389999999999999</v>
+        <v>-0.7255</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5319</v>
+        <v>0.5547</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1982</v>
+        <v>0.5947</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7929</v>
+        <v>1.5858</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.073</v>
+        <v>-0.636</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3158</v>
+        <v>-0.5743</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3888</v>
+        <v>-0.0616</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1476</v>
+        <v>-0.6036</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2666</v>
+        <v>1.8107</v>
       </c>
       <c r="X6" t="n">
         <v>-2.4142</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8797</v>
+        <v>-0.676</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.122</v>
+        <v>-1.9182</v>
       </c>
       <c r="F7" t="n">
         <v>1.2422</v>
@@ -1000,10 +1000,10 @@
         <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2093</v>
+        <v>-0.0055</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3744</v>
+        <v>-0.1706</v>
       </c>
       <c r="U7" t="n">
         <v>0.1651</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MUNOZ LEIVA</t>
+          <t>P. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1517</v>
+        <v>-0.849</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1549</v>
+        <v>2.6039</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3067</v>
+        <v>-3.4529</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7643</v>
+        <v>1.6831</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0167</v>
+        <v>-0.9188</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2525</v>
+        <v>2.602</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4232</v>
+        <v>3.154</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1822</v>
+        <v>0.0202</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2411</v>
+        <v>3.1339</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1875</v>
+        <v>-1.4709</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1989</v>
+        <v>-0.9389999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0114</v>
+        <v>-0.5319</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3964</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1805</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>1.784</v>
+        <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6829</v>
+        <v>-0.1862</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1125</v>
+        <v>0.1744</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4295</v>
+        <v>-0.3607</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.674</v>
+        <v>-2.1476</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7997</v>
+        <v>0.2666</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4737</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. MORENO MORALES</t>
+          <t>J. MUNOZ LEIVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4196</v>
+        <v>-1.4987</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2746</v>
+        <v>-0.4728</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.145</v>
+        <v>-1.0259</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0169</v>
+        <v>-0.7643</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1762</v>
+        <v>-1.0167</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1931</v>
+        <v>0.2525</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1538</v>
+        <v>0.4232</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9016</v>
+        <v>0.1822</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7478</v>
+        <v>0.2411</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1708</v>
+        <v>-1.1875</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7255</v>
+        <v>-1.1989</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5547</v>
+        <v>0.0114</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>-2.1805</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5858</v>
+        <v>1.784</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3938</v>
+        <v>0.3359</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2479</v>
+        <v>0.4847</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1459</v>
+        <v>-0.1488</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6036</v>
+        <v>-0.674</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8107</v>
+        <v>0.7997</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4142</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4742</v>
+        <v>-3.4897</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7221</v>
+        <v>-1.8218</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7521</v>
+        <v>-1.6679</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3007</v>
@@ -1234,13 +1234,13 @@
         <v>1.784</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1735</v>
+        <v>-0.189</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2993</v>
+        <v>-0.399</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1258</v>
+        <v>0.21</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6036</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3928</v>
+        <v>-6.5632</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.4062</v>
+        <v>-6.6889</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0133</v>
+        <v>0.1257</v>
       </c>
       <c r="G11" t="n">
         <v>-4.4901</v>
@@ -1312,13 +1312,13 @@
         <v>1.9822</v>
       </c>
       <c r="S11" t="n">
-        <v>0.13</v>
+        <v>-0.0403</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2572</v>
+        <v>-0.0255</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1271</v>
+        <v>-0.0148</v>
       </c>
       <c r="V11" t="n">
         <v>0.9405</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.9101</v>
+        <v>-8.9742</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.5099</v>
+        <v>-13.5738</v>
       </c>
       <c r="F12" t="n">
-        <v>4.5994</v>
+        <v>4.599500000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-4.8092</v>
@@ -1369,7 +1369,7 @@
         <v>-2.1551</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.8786</v>
+        <v>-0.8786000000000005</v>
       </c>
       <c r="M12" t="n">
         <v>-1.775200000000001</v>
@@ -1390,13 +1390,13 @@
         <v>14.8667</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1653000000000001</v>
+        <v>1.1014</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4578</v>
+        <v>-1.5219</v>
       </c>
       <c r="U12" t="n">
-        <v>2.6234</v>
+        <v>2.6233</v>
       </c>
       <c r="V12" t="n">
         <v>-3.2844</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.2899</v>
+        <v>7.6223</v>
       </c>
       <c r="E13" t="n">
         <v>3.7289</v>
       </c>
       <c r="F13" t="n">
-        <v>3.561</v>
+        <v>3.8933</v>
       </c>
       <c r="G13" t="n">
         <v>4.337</v>
@@ -1468,13 +1468,13 @@
         <v>2.7751</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0576</v>
+        <v>0.39</v>
       </c>
       <c r="T13" t="n">
         <v>-0.11</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1676</v>
+        <v>0.5</v>
       </c>
       <c r="V13" t="n">
         <v>2.1024</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1293</v>
+        <v>5.8822</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9744</v>
+        <v>2.4838</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1548</v>
+        <v>3.3984</v>
       </c>
       <c r="G14" t="n">
         <v>0.2279</v>
@@ -1546,13 +1546,13 @@
         <v>2.7751</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7199</v>
+        <v>0.033</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9139</v>
+        <v>-0.4045</v>
       </c>
       <c r="U14" t="n">
-        <v>0.194</v>
+        <v>0.4376</v>
       </c>
       <c r="V14" t="n">
         <v>4.8284</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. MORTELLARO</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.967</v>
+        <v>2.0638</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5775</v>
+        <v>-0.6187</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3894</v>
+        <v>2.6825</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1488</v>
+        <v>3.2477</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.5384</v>
+        <v>3.5769</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.3292</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.5798</v>
+        <v>3.1318</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.62</v>
+        <v>3.0877</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0402</v>
+        <v>0.0441</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.569</v>
+        <v>0.1159</v>
       </c>
       <c r="N15" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.4891</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6506</v>
+        <v>-0.3733</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7929</v>
+        <v>-1.784</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9911</v>
+        <v>-3.9645</v>
       </c>
       <c r="R15" t="n">
-        <v>1.784</v>
+        <v>2.1805</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8383</v>
+        <v>0.067</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1307</v>
+        <v>-0.3192</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7075</v>
+        <v>0.3862</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4846</v>
+        <v>0.5331</v>
       </c>
       <c r="W15" t="n">
-        <v>3.0178</v>
+        <v>0.5331</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>C. MORTELLARO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0993</v>
+        <v>2.0528</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0262</v>
+        <v>0.8645</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1255</v>
+        <v>1.1883</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2477</v>
+        <v>-2.1488</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5769</v>
+        <v>-1.5384</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3292</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1318</v>
+        <v>-1.5798</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0877</v>
+        <v>-1.62</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0441</v>
+        <v>0.0402</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1159</v>
+        <v>-0.569</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4891</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3733</v>
+        <v>-0.6506</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.784</v>
+        <v>0.7929</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.9645</v>
+        <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1805</v>
+        <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8975</v>
+        <v>0.9241</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7267</v>
+        <v>0.4176</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1708</v>
+        <v>0.5064</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5331</v>
+        <v>2.4846</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5331</v>
+        <v>3.0178</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. LÓPEZ GÓMEZ</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6027</v>
+        <v>0.9055</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6027</v>
+        <v>-1.0845</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6027</v>
+        <v>2.1641</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1.2574</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6027</v>
+        <v>0.9067</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6027</v>
+        <v>0.7866</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.7062</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6027</v>
+        <v>0.0804</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.3775</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.5512</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.8264</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.4047</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.8799</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.4752</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.4485</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.4485</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>P. LÓPEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5202</v>
+        <v>0.6027</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3901</v>
+        <v>0.6027</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9103</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1641</v>
+        <v>0.6027</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2574</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9067</v>
+        <v>0.6027</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7866</v>
+        <v>0.6027</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7062</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0804</v>
+        <v>0.6027</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3775</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5512</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8264</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.79</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1855</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3956</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4485</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.6871</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3248</v>
+        <v>-1.1211</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4059</v>
+        <v>0.434</v>
       </c>
       <c r="G20" t="n">
         <v>1.3734</v>
@@ -2014,13 +2014,13 @@
         <v>0.5947</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3264</v>
+        <v>-0.0945</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5616</v>
+        <v>-0.3578</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2352</v>
+        <v>0.2633</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5784</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. ZARACHO PAEZ</t>
+          <t>J. AGUERA ZEA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2806</v>
+        <v>-1.4607</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.334</v>
+        <v>-2.0255</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9465</v>
+        <v>0.5648</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0461</v>
+        <v>-1.4771</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1762</v>
+        <v>0.5201</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1301</v>
+        <v>-1.9972</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0404</v>
+        <v>-2.0493</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0404</v>
+        <v>0.1009</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-2.1501</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0057</v>
+        <v>0.5722</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1358</v>
+        <v>0.4193</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1301</v>
+        <v>0.1529</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5183</v>
+        <v>-0.5011</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6167</v>
+        <v>-0.5798</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0984</v>
+        <v>0.0788</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4485</v>
+        <v>-0.8701</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4485</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3514</v>
+        <v>-1.5316</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0174</v>
+        <v>-3.2212</v>
       </c>
       <c r="F22" t="n">
-        <v>1.666</v>
+        <v>1.6895</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6016</v>
@@ -2170,13 +2170,13 @@
         <v>1.1893</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2481</v>
+        <v>0.0679</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0696</v>
+        <v>-0.2734</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3178</v>
+        <v>0.3413</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1962</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. AGUERA ZEA</t>
+          <t>O. ZARACHO PAEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0602</v>
+        <v>-1.6319</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.433</v>
+        <v>-0.7415</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3729</v>
+        <v>-0.8904</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4771</v>
+        <v>0.0461</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5201</v>
+        <v>0.1762</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9972</v>
+        <v>-0.1301</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.0493</v>
+        <v>0.0404</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1009</v>
+        <v>0.0404</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.1501</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5722</v>
+        <v>0.0057</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4193</v>
+        <v>0.1358</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1529</v>
+        <v>-0.1301</v>
       </c>
       <c r="P23" t="n">
-        <v>1.3876</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1005</v>
+        <v>0.167</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9873</v>
+        <v>0.2093</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1132</v>
+        <v>-0.0422</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8701</v>
+        <v>-1.4485</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4737</v>
+        <v>-1.4485</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3898</v>
+        <v>-2.8521</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2601</v>
+        <v>-3.7694</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8703</v>
+        <v>0.9173</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2649</v>
@@ -2326,13 +2326,13 @@
         <v>1.9822</v>
       </c>
       <c r="S24" t="n">
-        <v>1.0065</v>
+        <v>0.5442</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1837</v>
+        <v>-0.3256</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8227</v>
+        <v>0.8698</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1225</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.9102</v>
+        <v>11.2686</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.599399999999999</v>
+        <v>-4.5993</v>
       </c>
       <c r="F25" t="n">
-        <v>14.5096</v>
+        <v>15.8677</v>
       </c>
       <c r="G25" t="n">
-        <v>4.8092</v>
+        <v>4.809200000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>8.0908</v>
+        <v>8.090799999999998</v>
       </c>
       <c r="I25" t="n">
         <v>-3.2815</v>
@@ -2380,7 +2380,7 @@
         <v>1.775300000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>5.935600000000001</v>
+        <v>5.9356</v>
       </c>
       <c r="L25" t="n">
         <v>-4.1601</v>
@@ -2404,13 +2404,13 @@
         <v>16.849</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1655000000000002</v>
+        <v>1.1929</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.6235</v>
+        <v>-2.6233</v>
       </c>
       <c r="U25" t="n">
-        <v>2.458</v>
+        <v>3.8164</v>
       </c>
       <c r="V25" t="n">
         <v>3.2843</v>
